--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_243_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_243_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M2" t="n">
         <v>12</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M3" t="n">
         <v>12</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1338,7 +1338,7 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1727,7 +1727,7 @@
         <v>4</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -2321,10 +2321,10 @@
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2511,7 +2511,7 @@
         <v>5</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
         <v>2</v>
@@ -2707,7 +2707,7 @@
         <v>16</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -3102,7 +3102,7 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -3301,10 +3301,10 @@
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X27" t="n">
         <v>2</v>
@@ -3827,16 +3827,16 @@
         <v>70</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U30" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X30" t="n">
         <v>15</v>
@@ -4488,7 +4488,7 @@
         <v>3</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -4886,10 +4886,10 @@
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X38" t="n">
         <v>0</v>
@@ -5076,10 +5076,10 @@
         <v>6</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -5275,13 +5275,13 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X40" t="n">
         <v>2</v>
@@ -5468,7 +5468,7 @@
         <v>11</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
         <v>9</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
@@ -5863,13 +5863,13 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X43" t="n">
         <v>1</v>
@@ -6059,13 +6059,13 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X44" t="n">
         <v>0</v>
@@ -6392,16 +6392,16 @@
         <v>97</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="V46" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="W46" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="X46" t="n">
         <v>9</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_243_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_243_EL.xlsx
@@ -674,10 +674,10 @@
         <v>12</v>
       </c>
       <c r="N2" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="O2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="P2" t="n">
         <v>12</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>93.75</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>12</v>
       </c>
       <c r="N3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="P3" t="n">
         <v>23</v>
@@ -1347,14 +1347,14 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA17" t="n">
@@ -1739,14 +1739,14 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA19" t="n">
@@ -2719,10 +2719,10 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
@@ -3307,14 +3307,14 @@
         <v>2</v>
       </c>
       <c r="X27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA27" t="n">
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
@@ -3839,14 +3839,14 @@
         <v>3</v>
       </c>
       <c r="X30" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="Y30" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>93.8%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -4304,14 +4304,14 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA35" t="n">
@@ -5284,14 +5284,14 @@
         <v>2</v>
       </c>
       <c r="X40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA40" t="n">
@@ -5480,10 +5480,10 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
@@ -6404,10 +6404,10 @@
         <v>5</v>
       </c>
       <c r="X46" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Y46" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
